--- a/docs/pacha-deportes-google-sheets-maestro.xlsx
+++ b/docs/pacha-deportes-google-sheets-maestro.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INICIO" sheetId="1" r:id="R8963fbddc21d4a37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="2" r:id="R812b4fd667ad411e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categorias" sheetId="3" r:id="R3beecfbbee664fc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usuarios" sheetId="4" r:id="R27cbb8e5b6a1499b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entrenadores" sheetId="5" r:id="R1e802a4c458b4d0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipos" sheetId="6" r:id="R920638879ab346da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jugadores" sheetId="7" r:id="Rec64a011736e4f43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixture" sheetId="8" r:id="R301528e33d724ef5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Convocatorias" sheetId="9" r:id="Rfc1f4be7dde14087"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanciones" sheetId="10" r:id="Rc8cbb9f9d35f4d25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resultados_Log" sheetId="11" r:id="Rdc8d3140c46d4d37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INICIO" sheetId="1" r:id="R1857825dbc294bdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="2" r:id="Rd24ecac168e0436d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categorias" sheetId="3" r:id="R550de36866ce4453"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usuarios" sheetId="4" r:id="R6d68ef86398845a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entrenadores" sheetId="5" r:id="Rcbaae0d268cd422c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipos" sheetId="6" r:id="R38420f9b914a474a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jugadores" sheetId="7" r:id="Raf2f7dff6b2a47e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixture" sheetId="8" r:id="R854a728562a54df0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Convocatorias" sheetId="9" r:id="R551c85db482148db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanciones" sheetId="10" r:id="R081b97727f594864"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resultados_Log" sheetId="11" r:id="Rad2bbb080ce9475f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -47,7 +47,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -64,6 +64,11 @@
         <x:fgColor rgb="7FB515"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="071225"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -72,7 +77,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -102,6 +107,15 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -523,6 +537,38 @@
         <x:v>Tarjetas y suspensiones</x:v>
       </x:c>
     </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Actualización</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Se agregaron columnas firstName, lastName y documentType en Jugadores.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Fotos/escudos</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Usar URL pública o ruta en GitHub Pages. Para subir directo a Drive se requiere endpoint adicional.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Jugadores</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Máximo 15 jugadores por categoría.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>Convocatorias</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>Se guardan en la hoja Convocatorias desde el panel entrenador.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
@@ -574,7 +620,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refca139153334c71"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf290155f35c4916"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -618,7 +664,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72236bd78522427f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a1ea8b6c6d540e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -690,7 +736,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64df54a17dd1453c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f69dada29634e91"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -894,7 +940,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raaf8a50ad14e4f04"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27ab3db8232c4e35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1549,7 +1595,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3060145339ce4995"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d45539e46a44fa0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2249,7 +2295,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R869f3df16ba44293"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ef73a6790b34ace"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2637,7 +2683,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcca6ef4d9c514559"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41f3fee30d5c4750"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2646,44 +2692,56 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="6.590000152587891" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="5.789999961853027" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.289999961853027" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="8.479999542236328" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="21.1299991607666" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16.149999618530273" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="7.940000057220459" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9.149999618530273" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10.5" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="12.25" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="29.8799991607666" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="7.940000057220459" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="10.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="8.079999923706055" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="7.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12.109999656677246" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="14" t="str">
+      <x:c r="A1" s="19" t="str">
         <x:v>playerId</x:v>
       </x:c>
-      <x:c r="B1" s="14" t="str">
+      <x:c r="B1" s="19" t="str">
         <x:v>teamId</x:v>
       </x:c>
-      <x:c r="C1" s="14" t="str">
+      <x:c r="C1" s="19" t="str">
         <x:v>teamName</x:v>
       </x:c>
-      <x:c r="D1" s="14" t="str">
+      <x:c r="D1" s="19" t="str">
         <x:v>fullName</x:v>
       </x:c>
-      <x:c r="E1" s="14" t="str">
+      <x:c r="E1" s="19" t="str">
         <x:v>dni</x:v>
       </x:c>
-      <x:c r="F1" s="14" t="str">
+      <x:c r="F1" s="19" t="str">
         <x:v>birthDate</x:v>
       </x:c>
-      <x:c r="G1" s="14" t="str">
+      <x:c r="G1" s="19" t="str">
         <x:v>categories</x:v>
       </x:c>
-      <x:c r="H1" s="14" t="str">
+      <x:c r="H1" s="19" t="str">
         <x:v>photoUrl</x:v>
       </x:c>
-      <x:c r="I1" s="14" t="str">
+      <x:c r="I1" s="19" t="str">
         <x:v>createdAt</x:v>
+      </x:c>
+      <x:c r="J1" s="22" t="str">
+        <x:v>firstName</x:v>
+      </x:c>
+      <x:c r="K1" s="22" t="str">
+        <x:v>lastName</x:v>
+      </x:c>
+      <x:c r="L1" s="22" t="str">
+        <x:v>documentType</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -2824,7 +2882,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9147cf72041749db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra829cc4709ec47d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4236,7 +4294,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8484028c48849ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R383553646814403b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4284,7 +4342,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2abddaa7f3b54554"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raeaae7cc0bd9452a"/>
   </x:tableParts>
 </x:worksheet>
 </file>